--- a/template.xlsx
+++ b/template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\paula\OneDrive\Desktop\TER_project-1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2EB7D19-AB69-4CD0-9FDD-C6D64B80AA53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5A18376-38ED-4964-9B78-9A4099FAE3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5580" yWindow="4530" windowWidth="21600" windowHeight="11295" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Faculty" sheetId="28" r:id="rId1"/>
@@ -2223,7 +2223,7 @@
     <xf numFmtId="43" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="522">
+  <cellXfs count="523">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -3623,6 +3623,9 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -3653,11 +3656,11 @@
 </file>
 
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="4" dropStyle="combo" dx="31" fmlaLink="Rank_Link" fmlaRange="Rank" sel="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="4" dropStyle="combo" dx="31" fmlaLink="Rank_Link" fmlaRange="Rank" sel="2" val="0"/>
 </file>
 
 <file path=xl/ctrlProps/ctrlProp2.xml><?xml version="1.0" encoding="utf-8"?>
-<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="6" dropStyle="combo" dx="31" fmlaLink="SubRank_Link" fmlaRange="SubRank" sel="1" val="0"/>
+<formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Drop" dropLines="6" dropStyle="combo" dx="31" fmlaLink="SubRank_Link" fmlaRange="SubRank" sel="2" val="0"/>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5677,6 +5680,13 @@
           </a:ext>
         </a:extLst>
       </xdr:spPr>
+      <xdr:txBody>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -7214,21 +7224,23 @@
       <c r="H26" s="161"/>
       <c r="I26" s="161"/>
       <c r="J26" s="161"/>
-      <c r="K26" s="344">
-        <v>10</v>
+      <c r="K26" s="522">
+        <f>TER!H25</f>
+        <v>0</v>
       </c>
       <c r="L26" s="344"/>
       <c r="M26" s="344"/>
       <c r="N26" s="161"/>
       <c r="O26" s="348">
+        <f>TER!J25</f>
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="P26" s="348"/>
       <c r="Q26" s="348"/>
       <c r="R26" s="161"/>
-      <c r="S26" s="344">
-        <f>K26*0.075</f>
-        <v>0.75</v>
+      <c r="S26" s="345">
+        <f>TER!L25</f>
+        <v>0</v>
       </c>
       <c r="T26" s="344"/>
       <c r="U26" s="161"/>
@@ -7247,21 +7259,23 @@
       <c r="H27" s="161"/>
       <c r="I27" s="161"/>
       <c r="J27" s="161"/>
-      <c r="K27" s="344">
-        <v>10</v>
+      <c r="K27" s="522">
+        <f>TER!H26</f>
+        <v>0</v>
       </c>
       <c r="L27" s="344"/>
       <c r="M27" s="344"/>
       <c r="N27" s="161"/>
       <c r="O27" s="348">
+        <f>TER!J26</f>
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="P27" s="348"/>
       <c r="Q27" s="348"/>
       <c r="R27" s="161"/>
-      <c r="S27" s="344">
-        <f>K27*0.075</f>
-        <v>0.75</v>
+      <c r="S27" s="345">
+        <f>TER!L26</f>
+        <v>0</v>
       </c>
       <c r="T27" s="344"/>
       <c r="U27" s="161"/>
@@ -7280,21 +7294,23 @@
       <c r="H28" s="161"/>
       <c r="I28" s="161"/>
       <c r="J28" s="161"/>
-      <c r="K28" s="344">
-        <v>8</v>
+      <c r="K28" s="522">
+        <f>TER!H27</f>
+        <v>0</v>
       </c>
       <c r="L28" s="344"/>
       <c r="M28" s="344"/>
       <c r="N28" s="161"/>
       <c r="O28" s="348">
+        <f>TER!J27</f>
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="P28" s="348"/>
       <c r="Q28" s="348"/>
       <c r="R28" s="161"/>
-      <c r="S28" s="344">
-        <f>K28*0.075</f>
-        <v>0.6</v>
+      <c r="S28" s="345">
+        <f>TER!L27</f>
+        <v>0</v>
       </c>
       <c r="T28" s="344"/>
       <c r="U28" s="161"/>
@@ -7313,21 +7329,23 @@
       <c r="H29" s="161"/>
       <c r="I29" s="161"/>
       <c r="J29" s="161"/>
-      <c r="K29" s="344">
-        <v>10</v>
+      <c r="K29" s="522">
+        <f>TER!H28</f>
+        <v>0</v>
       </c>
       <c r="L29" s="344"/>
       <c r="M29" s="344"/>
       <c r="N29" s="161"/>
       <c r="O29" s="348">
+        <f>TER!J28</f>
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="P29" s="348"/>
       <c r="Q29" s="348"/>
       <c r="R29" s="161"/>
-      <c r="S29" s="344">
-        <f>K29*0.075</f>
-        <v>0.75</v>
+      <c r="S29" s="345">
+        <f>TER!L28</f>
+        <v>0</v>
       </c>
       <c r="T29" s="344"/>
       <c r="U29" s="161"/>
@@ -7346,7 +7364,10 @@
       <c r="H30" s="161"/>
       <c r="I30" s="161"/>
       <c r="J30" s="161"/>
-      <c r="K30" s="344"/>
+      <c r="K30" s="522">
+        <f>TER!H29</f>
+        <v>0</v>
+      </c>
       <c r="L30" s="344"/>
       <c r="M30" s="344"/>
       <c r="N30" s="161"/>
@@ -7356,7 +7377,10 @@
       <c r="P30" s="346"/>
       <c r="Q30" s="346"/>
       <c r="R30" s="161"/>
-      <c r="S30" s="344"/>
+      <c r="S30" s="345">
+        <f>TER!L29</f>
+        <v>0</v>
+      </c>
       <c r="T30" s="344"/>
       <c r="U30" s="161"/>
       <c r="X30" s="317"/>
@@ -7374,7 +7398,10 @@
       <c r="H31" s="161"/>
       <c r="I31" s="161"/>
       <c r="J31" s="161"/>
-      <c r="K31" s="344"/>
+      <c r="K31" s="522">
+        <f>TER!H30</f>
+        <v>0</v>
+      </c>
       <c r="L31" s="344"/>
       <c r="M31" s="344"/>
       <c r="N31" s="161"/>
@@ -7384,7 +7411,10 @@
       <c r="P31" s="346"/>
       <c r="Q31" s="346"/>
       <c r="R31" s="161"/>
-      <c r="S31" s="344"/>
+      <c r="S31" s="345">
+        <f>TER!L30</f>
+        <v>0</v>
+      </c>
       <c r="T31" s="344"/>
       <c r="U31" s="161"/>
       <c r="X31" s="317"/>
@@ -11099,7 +11129,7 @@
       </c>
       <c r="C13" s="408" t="str">
         <f>DATA!M3 &amp; " " &amp;DATA!M4</f>
-        <v>Instructor I</v>
+        <v>Asst. Professor II</v>
       </c>
       <c r="D13" s="408"/>
       <c r="E13" s="408"/>
@@ -11213,7 +11243,7 @@
       </c>
       <c r="C22" s="81">
         <f>INDEX(Instruction,Rank_Link)</f>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D22" s="74" t="e">
         <f>C22*G22</f>
@@ -11455,7 +11485,7 @@
       </c>
       <c r="C36" s="81">
         <f>INDEX(Extension,Rank_Link)</f>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="D36" s="74">
         <f>C36*G36</f>
@@ -11789,7 +11819,7 @@
       </c>
       <c r="E13" s="408" t="str">
         <f>DATA!M3 &amp; " " &amp;DATA!M4</f>
-        <v>Instructor I</v>
+        <v>Asst. Professor II</v>
       </c>
       <c r="F13" s="408"/>
       <c r="G13" s="408"/>
@@ -12035,7 +12065,7 @@
       </c>
       <c r="C23" s="294">
         <f>'03'!C22</f>
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D23" s="145"/>
       <c r="E23" s="211"/>
@@ -12455,7 +12485,7 @@
       </c>
       <c r="C41" s="294">
         <f>'03'!C36</f>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="D41" s="145"/>
       <c r="E41" s="211"/>
@@ -12940,7 +12970,7 @@
         <v>72</v>
       </c>
       <c r="I3" s="516">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J3" s="410"/>
       <c r="K3" s="283" t="s">
@@ -12948,13 +12978,13 @@
       </c>
       <c r="M3" s="517" t="str">
         <f>INDEX(Rank, Rank_Link)</f>
-        <v>Instructor</v>
+        <v>Asst. Professor</v>
       </c>
       <c r="N3" s="518"/>
     </row>
     <row r="4" spans="2:14" ht="13.5" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="77">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" s="86" t="s">
         <v>65</v>
@@ -12970,7 +13000,7 @@
       </c>
       <c r="M4" s="519" t="str">
         <f>INDEX(SubRank, SubRank_Link)</f>
-        <v>I</v>
+        <v>II</v>
       </c>
       <c r="N4" s="520"/>
     </row>
@@ -13256,7 +13286,7 @@
       </c>
       <c r="F23" s="215">
         <f>'03'!C36</f>
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G23" s="216">
         <f>'03'!C43</f>
@@ -36586,60 +36616,52 @@
       <c r="B25" t="s">
         <v>158</v>
       </c>
-      <c r="H25" s="258">
-        <v>8</v>
-      </c>
+      <c r="H25" s="258"/>
       <c r="J25" s="322">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="L25" s="276">
         <f t="shared" ref="L25:L30" si="0">H25*J25</f>
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B26" t="s">
         <v>159</v>
       </c>
-      <c r="H26" s="258">
-        <v>8</v>
-      </c>
+      <c r="H26" s="258"/>
       <c r="J26" s="322">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="L26" s="276">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B27" t="s">
         <v>160</v>
       </c>
-      <c r="H27" s="258">
-        <v>8</v>
-      </c>
+      <c r="H27" s="258"/>
       <c r="J27" s="322">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="L27" s="276">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>161</v>
       </c>
-      <c r="H28" s="258">
-        <v>8</v>
-      </c>
+      <c r="H28" s="258"/>
       <c r="J28" s="322">
         <v>7.4999999999999997E-2</v>
       </c>
       <c r="L28" s="276">
         <f t="shared" si="0"/>
-        <v>0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
